--- a/mappings/Standards-GS1/Standards-GS1.xlsx
+++ b/mappings/Standards-GS1/Standards-GS1.xlsx
@@ -550,12 +550,12 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Stable mapping identifier, e.g., DPP_DPPO_0001</t>
+          <t>Stable mapping identifier, e.g., GS1_0001</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>DPP|DPPO|CEON</t>
+          <t>DPP|DPPO|CEON|GS1</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>DPP|DPPO|CEON</t>
+          <t>DPP|DPPO|CEON|GS1</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">

--- a/mappings/Standards-GS1/Standards-GS1.xlsx
+++ b/mappings/Standards-GS1/Standards-GS1.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -830,7 +830,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GS1_0004</t>
+          <t>GS1_0005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>DPPO</t>
+          <t>CEON</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -870,17 +870,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>http://w3id.org/dppo/ontology/dpp-info/value</t>
+          <t>http://w3id.org/CEON/ontology/product/hasGlobalTradeItemNumber</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>dpp-info</t>
+          <t>ceon-product</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>hasGlobalTradeItemNumber</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -895,79 +895,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>DPPO provides no datatype property parallel to gs1:gtin. The literal-valued dpp-info:value is the closest available, although its semantic scope is broader and not specific to product identifiers. Stated in the GS1 section of the accompanying paper.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>GS1_0005</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>GS1</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>DataProperty</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>https://www.gs1.org/voc/gtin</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>gs1</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>gtin</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>CEON</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>DataProperty</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>http://w3id.org/CEON/ontology/product/hasGlobalTradeItemNumber</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>ceon-product</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>hasGlobalTradeItemNumber</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>equivalent_property</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>bidirectional</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>CEON already provides a literal-valued property for the GTIN, with range xsd:string and an rdfs:seeAlso reference to the GS1 GTIN standard, so the two capture the same lexical value. Stated as an equivalence in the GS1 section of the accompanying paper.</t>
+          <t>CEON provides a literal-valued property for the GTIN carrying an rdfs:seeAlso reference to the GS1 standard. The two are not interchangeable. gs1:gtin is declared functional and declares gs1:Product and schema:Product as conjunctive domains, while the CEON property imposes neither constraint, so an equivalence would transfer both to CEON. The more constrained GS1 property is therefore aligned as a subproperty of the less constrained CEON property. Stated in the section on semantic alignment with the GS1 family of standards in the accompanying paper.</t>
         </is>
       </c>
     </row>
